--- a/Thesis Forecasting/metadata/xgboost/validation_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/xgboost/validation_average_metrics.xlsx
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.451840791241192</v>
+        <v>3.419576431509979</v>
       </c>
       <c r="E2" t="n">
-        <v>1.71664344441512</v>
+        <v>1.699455653952136</v>
       </c>
       <c r="F2" t="n">
-        <v>2.769457742259154</v>
+        <v>2.686937387670291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9283584018428611</v>
+        <v>0.932564144329582</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
-        <v>1.744494832966965</v>
+        <v>1.403638972068982</v>
       </c>
       <c r="E3" t="n">
-        <v>1.620137456758978</v>
+        <v>1.291389617967789</v>
       </c>
       <c r="F3" t="n">
-        <v>4.236730177584649</v>
+        <v>4.10041242645813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8266824694896371</v>
+        <v>0.8376561047942912</v>
       </c>
     </row>
     <row r="4">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D4" t="n">
-        <v>1.71745827658513</v>
+        <v>1.298614718107114</v>
       </c>
       <c r="E4" t="n">
-        <v>1.382999808041294</v>
+        <v>1.190482377494922</v>
       </c>
       <c r="F4" t="n">
-        <v>3.902914547977252</v>
+        <v>3.196609837158374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9364120941983439</v>
+        <v>0.9573444348960065</v>
       </c>
     </row>
     <row r="5">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D5" t="n">
-        <v>4.180765718437955</v>
+        <v>3.981715159288837</v>
       </c>
       <c r="E5" t="n">
-        <v>1.479533045060711</v>
+        <v>1.418838059082079</v>
       </c>
       <c r="F5" t="n">
-        <v>2.188924444285949</v>
+        <v>2.102737943311137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.907936863415191</v>
+        <v>0.9150439077442523</v>
       </c>
     </row>
     <row r="6">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.664091660721063</v>
+        <v>2.615445612548182</v>
       </c>
       <c r="E6" t="n">
-        <v>4.047043590636704</v>
+        <v>3.923876505981132</v>
       </c>
       <c r="F6" t="n">
-        <v>7.62303727279962</v>
+        <v>7.440075999279395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.849384400566642</v>
+        <v>0.8565275179102061</v>
       </c>
     </row>
     <row r="7">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D7" t="n">
-        <v>4.083274772187985</v>
+        <v>3.666833690136424</v>
       </c>
       <c r="E7" t="n">
-        <v>1.314191121949027</v>
+        <v>1.171925912428912</v>
       </c>
       <c r="F7" t="n">
-        <v>2.057274702140808</v>
+        <v>1.89522074726815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.832767704050032</v>
+        <v>0.8580762150003438</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/xgboost/validation_average_metrics.xlsx
+++ b/Thesis Forecasting/metadata/xgboost/validation_average_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,37 +440,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
